--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484203_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484203_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1365</v>
+        <v>11.746</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5241</v>
+        <v>11.8068</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3877</v>
+        <v>-0.0608</v>
       </c>
       <c r="G2" t="n">
         <v>10.0227</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4287</v>
+        <v>0.1808</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1043</v>
+        <v>0.1783</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3243</v>
+        <v>0.0025</v>
       </c>
       <c r="V2" t="n">
         <v>2.7145</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.025</v>
+        <v>4.0523</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8688</v>
+        <v>3.5966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1562</v>
+        <v>0.4557</v>
       </c>
       <c r="G3" t="n">
         <v>4.7237</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3163</v>
+        <v>-0.2889</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.1196</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.469</v>
+        <v>-0.1694</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1638</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3694</v>
+        <v>2.7804</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1803</v>
+        <v>2.5641</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1891</v>
+        <v>0.2163</v>
       </c>
       <c r="G4" t="n">
         <v>2.2459</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3258</v>
+        <v>0.0853</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0438</v>
+        <v>0.34</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.282</v>
+        <v>-0.2547</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3321</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4539</v>
+        <v>1.4874</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2697</v>
+        <v>0.4175</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7236</v>
+        <v>1.0699</v>
       </c>
       <c r="G5" t="n">
         <v>5.0046</v>
@@ -844,13 +844,13 @@
         <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3757</v>
+        <v>0.4092</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5364</v>
+        <v>0.1508</v>
       </c>
       <c r="U5" t="n">
-        <v>0.912</v>
+        <v>0.2584</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9962</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.583</v>
+        <v>-0.0171</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5969</v>
+        <v>-0.0305</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0139</v>
+        <v>0.0134</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2851</v>
@@ -922,13 +922,13 @@
         <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0086</v>
+        <v>0.4085</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1228</v>
+        <v>0.4955</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1142</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0.6642</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1677</v>
+        <v>-0.8426</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.025</v>
+        <v>0.1367</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1427</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8978</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3285</v>
+        <v>-0.0034</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3631</v>
+        <v>-0.2015</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0346</v>
+        <v>0.1981</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3321</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5185</v>
+        <v>-1.4446</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7096</v>
+        <v>-1.6085</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1911</v>
+        <v>0.1639</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6309</v>
@@ -1078,13 +1078,13 @@
         <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3016</v>
+        <v>-0.2277</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.12</v>
+        <v>-0.1472</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5467</v>
+        <v>-2.356</v>
       </c>
       <c r="E9" t="n">
         <v>-1.8128</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7338</v>
+        <v>-0.5432</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7851</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1755</v>
+        <v>0.0151</v>
       </c>
       <c r="T9" t="n">
         <v>0.311</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4865</v>
+        <v>-0.2958</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0321</v>
+        <v>-5.1951</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2106</v>
+        <v>-4.0195</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8215</v>
+        <v>-1.1755</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8898</v>
@@ -1234,13 +1234,13 @@
         <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>1.588</v>
+        <v>0.425</v>
       </c>
       <c r="T10" t="n">
-        <v>0.864</v>
+        <v>0.0551</v>
       </c>
       <c r="U10" t="n">
-        <v>0.724</v>
+        <v>0.3699</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9955</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.302800000000001</v>
+        <v>10.2107</v>
       </c>
       <c r="E11" t="n">
-        <v>10.1424</v>
+        <v>11.0504</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8396</v>
+        <v>-0.8395999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>16.5082</v>
@@ -1312,13 +1312,13 @@
         <v>11.7205</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09589999999999987</v>
+        <v>1.0039</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2212999999999999</v>
+        <v>1.1291</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1253999999999998</v>
+        <v>-0.1250999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.441</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2331</v>
+        <v>1.9915</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2755</v>
+        <v>2.6319</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0424</v>
+        <v>-0.6405</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5729</v>
+        <v>0.9218</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8437</v>
+        <v>0.6526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7292</v>
+        <v>0.2692</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6427</v>
+        <v>1.6807</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5617</v>
+        <v>1.6807</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2156</v>
+        <v>-0.7589</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4055</v>
+        <v>-1.0281</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8101</v>
+        <v>0.2692</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3567</v>
+        <v>1.0613</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3872</v>
+        <v>0.7093</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0305</v>
+        <v>0.3521</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8865</v>
+        <v>-1.1638</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2224</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6642</v>
+        <v>-2.3824</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8627</v>
+        <v>1.534</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3397</v>
+        <v>1.8488</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4771</v>
+        <v>-0.3148</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9218</v>
+        <v>-1.5729</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6526</v>
+        <v>-0.8437</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2692</v>
+        <v>-0.7292</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6807</v>
+        <v>1.6427</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6807</v>
+        <v>1.5617</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7589</v>
+        <v>-3.2156</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0281</v>
+        <v>-2.4055</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2692</v>
+        <v>-0.8101</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9326</v>
+        <v>0.6576</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4171</v>
+        <v>0.9604</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5155</v>
+        <v>-0.3028</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1638</v>
+        <v>0.8865</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0.2224</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3824</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0346</v>
+        <v>1.3735</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3975</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6371</v>
+        <v>0.5827</v>
       </c>
       <c r="G14" t="n">
         <v>0.4044</v>
@@ -1546,13 +1546,13 @@
         <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2981</v>
+        <v>0.637</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8035</v>
+        <v>0.1968</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4946</v>
+        <v>0.4401</v>
       </c>
       <c r="V14" t="n">
         <v>0.3321</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.6866</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1807</v>
+        <v>-0.0796</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6615</v>
+        <v>-0.607</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0271</v>
@@ -1624,13 +1624,13 @@
         <v>0.3907</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2058</v>
+        <v>-0.0502</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4267</v>
+        <v>-1.0379</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0631</v>
+        <v>-0.4564</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3636</v>
+        <v>-0.5814</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6849</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6516</v>
+        <v>-0.2628</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0289</v>
+        <v>-0.4222</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3773</v>
+        <v>0.1594</v>
       </c>
       <c r="V16" t="n">
         <v>0.8865</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7721</v>
+        <v>-1.4687</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.8058</v>
       </c>
       <c r="F17" t="n">
         <v>-2.2746</v>
@@ -1780,10 +1780,10 @@
         <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7538</v>
+        <v>-0.4505</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4153</v>
+        <v>-0.112</v>
       </c>
       <c r="U17" t="n">
         <v>-0.3385</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>Q. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6941</v>
+        <v>-1.9019</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0262</v>
+        <v>-0.6576</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3322</v>
+        <v>-1.2443</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1528</v>
+        <v>-4.9753</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1325</v>
+        <v>-2.9663</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.0203</v>
+        <v>-2.0091</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.8585</v>
+        <v>-1.2205</v>
       </c>
       <c r="K18" t="n">
-        <v>0.431</v>
+        <v>-0.426</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.2896</v>
+        <v>-0.7945</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2943</v>
+        <v>-3.7549</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5636</v>
+        <v>-2.5403</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2692</v>
+        <v>-1.2146</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7599</v>
+        <v>-0.1843</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3548</v>
+        <v>-0.1786</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4051</v>
+        <v>-0.0056</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2186</v>
+        <v>1.1089</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1638</v>
+        <v>1.7182</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0549</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q. ROIG GARCIA</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2787</v>
+        <v>-2.6124</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.871</v>
+        <v>-3.0262</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4077</v>
+        <v>0.4139</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.9753</v>
+        <v>-3.1528</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9663</v>
+        <v>-0.1325</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0091</v>
+        <v>-3.0203</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2205</v>
+        <v>-2.8585</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.426</v>
+        <v>0.431</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7945</v>
+        <v>-3.2896</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.7549</v>
+        <v>-0.2943</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.5403</v>
+        <v>-0.5636</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2146</v>
+        <v>0.2692</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1255</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5611</v>
+        <v>-0.6782</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.392</v>
+        <v>-0.3548</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.169</v>
+        <v>-0.3234</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1089</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7182</v>
+        <v>1.1638</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7569</v>
+        <v>-3.0409</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3847</v>
+        <v>-0.9366</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3721</v>
+        <v>-2.1043</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4172</v>
+        <v>-4.3413</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4889</v>
+        <v>-0.7271</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9283</v>
+        <v>-3.6143</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1283</v>
+        <v>0.0979</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1678</v>
+        <v>2.0926</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0395</v>
+        <v>-1.9947</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.5455</v>
+        <v>-4.4393</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6567</v>
+        <v>-2.8196</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8889</v>
+        <v>-1.6196</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>2.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5117</v>
+        <v>-0.6176</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5364</v>
+        <v>-0.2997</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0246</v>
+        <v>-0.318</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6628</v>
+        <v>-3.4535</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1499</v>
+        <v>-0.0814</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5128</v>
+        <v>-3.3721</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.3413</v>
+        <v>-2.4172</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7271</v>
+        <v>-0.4889</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6143</v>
+        <v>-1.9283</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0979</v>
+        <v>1.1283</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0926</v>
+        <v>1.1678</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9947</v>
+        <v>-0.0395</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.4393</v>
+        <v>-3.5455</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.8196</v>
+        <v>-1.6567</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6196</v>
+        <v>-1.8889</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9301</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2396</v>
+        <v>-0.2084</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5131</v>
+        <v>-0.233</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7265</v>
+        <v>0.0246</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9414</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.303100000000001</v>
+        <v>-9.302900000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.839599999999999</v>
+        <v>0.8394999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.1425</v>
+        <v>-10.1424</v>
       </c>
       <c r="G22" t="n">
         <v>-16.5082</v>
@@ -2149,7 +2149,7 @@
         <v>10.1021</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.0408</v>
+        <v>-4.040800000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-22.5699</v>
@@ -2170,13 +2170,13 @@
         <v>17.5809</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0961000000000003</v>
+        <v>-0.09610000000000027</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1251999999999998</v>
+        <v>0.1252000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2213000000000004</v>
+        <v>-0.2212999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>1.4409</v>
@@ -2185,7 +2185,7 @@
         <v>6.373200000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.932099999999999</v>
+        <v>-4.9321</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484203_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484203_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.9955</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,11 +1379,12 @@
       <c r="X11" t="n">
         <v>-6.3733</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1396,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9915</v>
+        <v>1.534</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6319</v>
+        <v>1.8488</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6405</v>
+        <v>-0.3148</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9218</v>
+        <v>-1.5729</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6526</v>
+        <v>-0.8437</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2692</v>
+        <v>-0.7292</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6807</v>
+        <v>1.6427</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6807</v>
+        <v>1.5617</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7589</v>
+        <v>-3.2156</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0281</v>
+        <v>-2.4055</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2692</v>
+        <v>-0.8101</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0613</v>
+        <v>0.6576</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7093</v>
+        <v>0.9604</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3521</v>
+        <v>-0.3028</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1638</v>
+        <v>0.8865</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0.2224</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3824</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.534</v>
+        <v>1.3735</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8488</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3148</v>
+        <v>0.5827</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5729</v>
+        <v>0.4044</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8437</v>
+        <v>0.9982</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7292</v>
+        <v>-0.5938</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6427</v>
+        <v>1.2935</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5617</v>
+        <v>1.2126</v>
       </c>
       <c r="L13" t="n">
         <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2156</v>
+        <v>-0.8891</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.4055</v>
+        <v>-0.2144</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8101</v>
+        <v>-0.6747</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5395</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6576</v>
+        <v>0.637</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9604</v>
+        <v>0.1968</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3028</v>
+        <v>0.4401</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8865</v>
+        <v>0.3321</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2224</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6642</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3735</v>
+        <v>1.0705</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7907999999999999</v>
+        <v>1.711</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5827</v>
+        <v>-0.6405</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4044</v>
+        <v>0.0009</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9982</v>
+        <v>-0.2684</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5938</v>
+        <v>0.2692</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2935</v>
+        <v>0.7598</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2126</v>
+        <v>0.7598</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8891</v>
+        <v>-0.7589</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2144</v>
+        <v>-1.0281</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6747</v>
+        <v>0.2692</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>0.637</v>
+        <v>1.0613</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1968</v>
+        <v>0.7093</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4401</v>
+        <v>0.3521</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3321</v>
+        <v>-1.1638</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0549</v>
+        <v>-2.3824</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6866</v>
+        <v>0.921</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0796</v>
+        <v>0.921</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.607</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0271</v>
+        <v>0.921</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7572</v>
+        <v>0.921</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2698</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0614</v>
+        <v>0.921</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0614</v>
+        <v>0.921</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0885</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8186</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2698</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0502</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.141</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09080000000000001</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1640,12 +1706,17 @@
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0379</v>
+        <v>-0.6866</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4564</v>
+        <v>-0.0796</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5814</v>
+        <v>-0.607</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6849</v>
+        <v>-1.0271</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7657</v>
+        <v>-0.7572</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08069999999999999</v>
+        <v>-0.2698</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0327</v>
+        <v>0.0614</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4119</v>
+        <v>0.0614</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7176</v>
+        <v>-1.0885</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1775</v>
+        <v>-0.8186</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5401</v>
+        <v>-0.2698</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2628</v>
+        <v>-0.0502</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4222</v>
+        <v>-0.141</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1594</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4687</v>
+        <v>-1.0379</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8058</v>
+        <v>-0.4564</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2746</v>
+        <v>-0.5814</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3371</v>
+        <v>-0.6849</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0131</v>
+        <v>-0.7657</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3502</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2033</v>
+        <v>1.0327</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9084</v>
+        <v>0.4119</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2949</v>
+        <v>0.6208</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8662</v>
+        <v>-1.7176</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9215</v>
+        <v>-1.1775</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9447</v>
+        <v>-0.5401</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4505</v>
+        <v>-0.2628</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.112</v>
+        <v>-0.4222</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3385</v>
+        <v>0.1594</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5507</v>
+        <v>0.8865</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3321</v>
+        <v>0.8865</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q. ROIG GARCIA</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9019</v>
+        <v>-1.4687</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6576</v>
+        <v>0.8058</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2443</v>
+        <v>-2.2746</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.9753</v>
+        <v>0.3371</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.9663</v>
+        <v>-0.0131</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0091</v>
+        <v>0.3502</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2205</v>
+        <v>3.2033</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.426</v>
+        <v>1.9084</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7945</v>
+        <v>1.2949</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.7549</v>
+        <v>-2.8662</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.5403</v>
+        <v>-1.9215</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2146</v>
+        <v>-0.9447</v>
       </c>
       <c r="P18" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.1488</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.1255</v>
-      </c>
       <c r="S18" t="n">
-        <v>-0.1843</v>
+        <v>-0.4505</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1786</v>
+        <v>-0.112</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0056</v>
+        <v>-0.3385</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1089</v>
+        <v>-1.5507</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7182</v>
+        <v>-0.3321</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>Q. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6124</v>
+        <v>-1.9019</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0262</v>
+        <v>-0.6576</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4139</v>
+        <v>-1.2443</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1528</v>
+        <v>-4.9753</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1325</v>
+        <v>-2.9663</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.0203</v>
+        <v>-2.0091</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.8585</v>
+        <v>-1.2205</v>
       </c>
       <c r="K19" t="n">
-        <v>0.431</v>
+        <v>-0.426</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.2896</v>
+        <v>-0.7945</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2943</v>
+        <v>-3.7549</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5636</v>
+        <v>-2.5403</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2692</v>
+        <v>-1.2146</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>3.1255</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6782</v>
+        <v>-0.1843</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3548</v>
+        <v>-0.1786</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3234</v>
+        <v>-0.0056</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>1.1089</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1638</v>
+        <v>1.7182</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0549</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0409</v>
+        <v>-2.6124</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9366</v>
+        <v>-3.0262</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1043</v>
+        <v>0.4139</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.3413</v>
+        <v>-3.1528</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7271</v>
+        <v>-0.1325</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.6143</v>
+        <v>-3.0203</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0979</v>
+        <v>-2.8585</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0926</v>
+        <v>0.431</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9947</v>
+        <v>-3.2896</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.4393</v>
+        <v>-0.2943</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.8196</v>
+        <v>-0.5636</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6196</v>
+        <v>0.2692</v>
       </c>
       <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.9767</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-1.9534</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.9301</v>
-      </c>
       <c r="S20" t="n">
-        <v>-0.6176</v>
+        <v>-0.6782</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2997</v>
+        <v>-0.3548</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.318</v>
+        <v>-0.3234</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9414</v>
+        <v>1.2186</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>1.1638</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4535</v>
+        <v>-3.0409</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0814</v>
+        <v>-0.9366</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3721</v>
+        <v>-2.1043</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4172</v>
+        <v>-4.3413</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4889</v>
+        <v>-0.7271</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9283</v>
+        <v>-3.6143</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1283</v>
+        <v>0.0979</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1678</v>
+        <v>2.0926</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0395</v>
+        <v>-1.9947</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.5455</v>
+        <v>-4.4393</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6567</v>
+        <v>-2.8196</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8889</v>
+        <v>-1.6196</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>2.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2084</v>
+        <v>-0.6176</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.233</v>
+        <v>-0.2997</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0246</v>
+        <v>-0.318</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>0.9414</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,152 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.302900000000001</v>
+        <v>-3.4535</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8394999999999999</v>
+        <v>-0.0814</v>
       </c>
       <c r="F22" t="n">
+        <v>-3.3721</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.4172</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.4889</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.9283</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.1283</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.1678</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.0395</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-3.5455</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.6567</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1.8889</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.2084</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.233</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484203_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-9.302899999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8395999999999992</v>
+      </c>
+      <c r="F23" t="n">
         <v>-10.1424</v>
       </c>
-      <c r="G22" t="n">
-        <v>-16.5082</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="G23" t="n">
+        <v>-16.5081</v>
+      </c>
+      <c r="H23" t="n">
         <v>-5.043699999999999</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>-11.4647</v>
       </c>
-      <c r="J22" t="n">
-        <v>6.061500000000001</v>
-      </c>
-      <c r="K22" t="n">
-        <v>10.1021</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J23" t="n">
+        <v>6.061600000000002</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10.1022</v>
+      </c>
+      <c r="L23" t="n">
         <v>-4.040800000000001</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>-22.5699</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>-15.1458</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>-7.424099999999999</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>5.8603</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>17.5809</v>
       </c>
-      <c r="S22" t="n">
-        <v>-0.09610000000000027</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.1252000000000001</v>
-      </c>
-      <c r="U22" t="n">
-        <v>-0.2212999999999999</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="S23" t="n">
+        <v>-0.09609999999999994</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1251999999999999</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.2213000000000001</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.4409</v>
       </c>
-      <c r="W22" t="n">
-        <v>6.373200000000001</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="W23" t="n">
+        <v>6.373199999999999</v>
+      </c>
+      <c r="X23" t="n">
         <v>-4.9321</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
